--- a/ksoft/docs/fields_details/Item_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Item_Fields_Detail.xlsx
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBB6B107-90A7-4658-919A-BF7E7AE0FE36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{684AB08E-AAD8-4284-A8C7-75BF16331876}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C800631F-19C3-47CE-BED2-A7DE2831F456}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38676BC1-9B65-4F12-8B92-167C0627FC1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BD15C18-9010-48F1-9EF4-0E2D25C798E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D6931F-FDC0-491C-9FC9-1B8DDD6A2C8D}"/>
 </file>
--- a/ksoft/docs/fields_details/Item_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Item_Fields_Detail.xlsx
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{684AB08E-AAD8-4284-A8C7-75BF16331876}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBB6B107-90A7-4658-919A-BF7E7AE0FE36}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38676BC1-9B65-4F12-8B92-167C0627FC1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C800631F-19C3-47CE-BED2-A7DE2831F456}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D6931F-FDC0-491C-9FC9-1B8DDD6A2C8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BD15C18-9010-48F1-9EF4-0E2D25C798E9}"/>
 </file>